--- a/Side Bar Files/GWD Data/Scaffolding.xlsx
+++ b/Side Bar Files/GWD Data/Scaffolding.xlsx
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_6" displayName="Table_6" ref="A1:D2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D2">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -556,7 +556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB887D7-B5A8-4A8C-A1C4-6A1EB884B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F70F55-CC75-4DCB-BA52-12E0C320B9A7}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Scaffolding.xlsx
+++ b/Side Bar Files/GWD Data/Scaffolding.xlsx
@@ -91,25 +91,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -130,11 +116,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -249,7 +235,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_7" displayName="Table_7" ref="A1:D2">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -556,7 +542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F70F55-CC75-4DCB-BA52-12E0C320B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562BE850-6A64-4B28-99CC-0D541BC5BAA6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Scaffolding.xlsx
+++ b/Side Bar Files/GWD Data/Scaffolding.xlsx
@@ -542,7 +542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562BE850-6A64-4B28-99CC-0D541BC5BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D55051-DFDA-4ED9-8946-41D4D206BAA6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Scaffolding.xlsx
+++ b/Side Bar Files/GWD Data/Scaffolding.xlsx
@@ -542,7 +542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D55051-DFDA-4ED9-8946-41D4D206BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C063C7-13B1-453F-B010-471D1BE4BAA6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
